--- a/ct/tests/fixtures/repository_cutover/workspace/excel/Quest.xlsx
+++ b/ct/tests/fixtures/repository_cutover/workspace/excel/Quest.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,15 +26,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Segoe UI"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="微软雅黑"/>
-      <i val="1"/>
-      <color rgb="00888888"/>
+      <name val="Aptos"/>
+      <color rgb="00334155"/>
       <sz val="9"/>
     </font>
   </fonts>
@@ -47,24 +40,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C9A227"/>
-        <bgColor rgb="00C9A227"/>
+        <fgColor rgb="0092400E"/>
+        <bgColor rgb="0092400E"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
-        <bgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00E2E8F0"/>
+        <bgColor rgb="00E2E8F0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001B4332"/>
-        <bgColor rgb="001B4332"/>
+        <fgColor rgb="00334155"/>
+        <bgColor rgb="00334155"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -78,21 +71,152 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="000F172A"/>
+      </left>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="medium">
+        <color rgb="000F172A"/>
+      </right>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="000F172A"/>
+      </left>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="double">
+        <color rgb="00334155"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="double">
+        <color rgb="00334155"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="medium">
+        <color rgb="000F172A"/>
+      </right>
+      <top style="thin"/>
+      <bottom style="double">
+        <color rgb="00334155"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin">
+        <color rgb="000F172A"/>
+      </right>
+      <top style="thin"/>
+      <bottom style="double">
+        <color rgb="00334155"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="000F172A"/>
+      </right>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="double">
+        <color rgb="00334155"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="000F172A"/>
+      </right>
+      <top style="thin"/>
+      <bottom style="double">
+        <color rgb="00334155"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin">
+        <color rgb="000F172A"/>
+      </right>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="000F172A"/>
+      </right>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -101,34 +225,20 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00EDF7EE"/>
-          <bgColor rgb="00EDF7EE"/>
+          <fgColor rgb="00F8FAFC"/>
+          <bgColor rgb="00F8FAFC"/>
         </patternFill>
       </fill>
-      <border>
-        <left style="thin">
-          <color rgb="00CCCCCC"/>
-        </left>
-        <right style="thin">
-          <color rgb="00CCCCCC"/>
-        </right>
-      </border>
     </dxf>
     <dxf>
+      <font>
+        <color rgb="00155E75"/>
+      </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00FFFFFF"/>
-          <bgColor rgb="00FFFFFF"/>
+          <fgColor rgb="00ECFEFF"/>
         </patternFill>
       </fill>
-      <border>
-        <left style="thin">
-          <color rgb="00CCCCCC"/>
-        </left>
-        <right style="thin">
-          <color rgb="00CCCCCC"/>
-        </right>
-      </border>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -492,7 +602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -500,66 +610,84 @@
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>任务唯一ID，禁止修改</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>任务标题（多语言）</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>任务描述（多语言）</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>奖励道具ID，关联 Item.Id</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>接取等级要求</t>
+        </is>
+      </c>
+      <c r="F1" s="9" t="inlineStr">
+        <is>
+          <t>测试测试</t>
+        </is>
+      </c>
+      <c r="G1" s="10" t="n"/>
+      <c r="H1" s="11" t="n"/>
+    </row>
+    <row r="2" ht="38" customHeight="1">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>Id
 int32</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>Title
-string[i18n]</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
+string</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>Description
-string[i18n]</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
+string</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>RewardItemId
-int32[ref:Item.Id]</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
+int32</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>RequiredLevel
 int32</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>任务唯一ID，禁止修改</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>任务标题（多语言）</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>任务描述（多语言）</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>奖励道具ID，关联 Item.Id</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>接取等级要求</t>
-        </is>
-      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>Test
+vector&lt;double&gt;</t>
+        </is>
+      </c>
+      <c r="G2" s="13" t="n"/>
+      <c r="H2" s="14" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -603,15 +731,97 @@
         <v>10</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>长标题</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>长描述</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A3:E1000">
+  <mergeCells count="2">
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="F1:H1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A3:A1048576">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" priority="2" dxfId="1">
-      <formula>MOD(ROW(),2)=1</formula>
+      <formula>AND($A3&lt;&gt;"",MOD(ROW(),2)=0)</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="B3:B1048576">
+    <cfRule type="expression" priority="2" dxfId="0">
+      <formula>AND($A3&lt;&gt;"",MOD(ROW(),2)=0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C3:C1048576">
+    <cfRule type="expression" priority="3" dxfId="0">
+      <formula>AND($A3&lt;&gt;"",MOD(ROW(),2)=0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D3:D1048576">
+    <cfRule type="expression" priority="4" dxfId="1">
+      <formula>D3&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E3:E1048576">
+    <cfRule type="expression" priority="5" dxfId="0">
+      <formula>AND($A3&lt;&gt;"",MOD(ROW(),2)=0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3:F1048576">
+    <cfRule type="expression" priority="6" dxfId="0">
+      <formula>AND($A3&lt;&gt;"",MOD(ROW(),2)=0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3:G1048576">
+    <cfRule type="expression" priority="7" dxfId="0">
+      <formula>AND($A3&lt;&gt;"",MOD(ROW(),2)=0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3:H1048576">
+    <cfRule type="expression" priority="8" dxfId="0">
+      <formula>AND($A3&lt;&gt;"",MOD(ROW(),2)=0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="6">
+    <dataValidation sqref="A3:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="between">
+      <formula1>-2147483648</formula1>
+      <formula2>2147483647</formula2>
+    </dataValidation>
+    <dataValidation sqref="D3:D1048576" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="引用" prompt="目标：Item.Id；最终以 canonical 校验为准" type="custom">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation sqref="E3:E1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="between">
+      <formula1>-2147483648</formula1>
+      <formula2>2147483647</formula2>
+    </dataValidation>
+    <dataValidation sqref="F3:F1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="decimal" operator="between">
+      <formula1>-1E+307</formula1>
+      <formula2>1E+307</formula2>
+    </dataValidation>
+    <dataValidation sqref="G3:G1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="decimal" operator="between">
+      <formula1>-1E+307</formula1>
+      <formula2>1E+307</formula2>
+    </dataValidation>
+    <dataValidation sqref="H3:H1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="decimal" operator="between">
+      <formula1>-1E+307</formula1>
+      <formula2>1E+307</formula2>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>